--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\89875\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC09F3DD-0864-4056-8520-F1100E96718C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B645A029-D914-4736-A3D0-AD065B6B1812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="硫化换模计划" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化换模计划!$A$4:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化换模计划!$A$5:$P$5</definedName>
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{4AD7BF10-0F75-4AD6-8D2F-7144E065D622}">
+    <comment ref="O4" authorId="0" shapeId="0" xr:uid="{4AD7BF10-0F75-4AD6-8D2F-7144E065D622}">
       <text>
         <r>
           <rPr>
@@ -69,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{3C6E1BD3-68BF-449A-A481-A550E4DD7874}">
+    <comment ref="P4" authorId="0" shapeId="0" xr:uid="{3C6E1BD3-68BF-449A-A481-A550E4DD7874}">
       <text>
         <r>
           <rPr>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t xml:space="preserve">序号
 </t>
@@ -777,6 +777,50 @@
   <si>
     <t>{version}</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>planDate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>classIndex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lhMachineName</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>planOrder</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>leftRightMould</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>beforeMaterialCode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>beforeMaterialDesc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>afterMaterialCode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>afterMaterialDesc</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>mouldCode</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>remark</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1225,13 +1269,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1564,7 +1608,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5546875" style="3" customWidth="1"/>
@@ -1584,191 +1628,226 @@
     <col min="17" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:16" ht="12" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="26"/>
     </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="30"/>
     </row>
-    <row r="3" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+    <row r="4" spans="1:16" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B4" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D4" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I4" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="22" t="s">
+      <c r="K4" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="L4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N4" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="21" t="s">
+      <c r="O4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P4" s="20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="37.799999999999997" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="5" spans="1:16" ht="37.799999999999997" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D5" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="J5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="16"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="14" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="23.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="6" spans="1:16" ht="23.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P4" xr:uid="{4349BEB0-D369-4858-9ED4-D698ADBC337B}"/>
+  <autoFilter ref="A5:P5" xr:uid="{4349BEB0-D369-4858-9ED4-D698ADBC337B}"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD0FCF7-DF9C-4266-847C-FC2472398FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2563EB-4E00-4F46-A3B6-63F46C49A7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="硫化换模计划" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化换模计划!$A$3:$P$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">硫化换模计划!$A$4:$P$4</definedName>
     <definedName name="A">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>干冰清洗</t>
   </si>
@@ -436,6 +436,54 @@
   </si>
   <si>
     <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{seq}</t>
+  </si>
+  <si>
+    <t>{planDate}</t>
+  </si>
+  <si>
+    <t>{classIndex}</t>
+  </si>
+  <si>
+    <t>{lhMachineCode}</t>
+  </si>
+  <si>
+    <t>{leftRightMould}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialCode}</t>
+  </si>
+  <si>
+    <t>{beforeMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialCode}</t>
+  </si>
+  <si>
+    <t>{afterMaterialDesc}</t>
+  </si>
+  <si>
+    <t>{afterMaterialType}</t>
+  </si>
+  <si>
+    <t>{endType}</t>
+  </si>
+  <si>
+    <t>{isDryIceClean}</t>
+  </si>
+  <si>
+    <t>{isSandblastingClean}</t>
+  </si>
+  <si>
+    <t>{isReplaceBlock}</t>
+  </si>
+  <si>
+    <t>{mouldCode}</t>
+  </si>
+  <si>
+    <t>{remark}</t>
   </si>
 </sst>
 </file>
@@ -677,13 +725,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>51767</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>20706</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>279538</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>407495</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1016,7 +1064,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="14" customWidth="1" collapsed="1"/>
@@ -1036,178 +1084,228 @@
     <col min="19" max="16384" width="8.88671875" style="6" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="33.75" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+    <row r="1" spans="1:16" hidden="1">
+      <c r="A1" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="33.75" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="5"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="5"/>
     </row>
-    <row r="2" spans="1:16" s="8" customFormat="1" ht="34.200000000000003" customHeight="1">
-      <c r="A2" s="7" t="s">
+    <row r="3" spans="1:16" s="8" customFormat="1" ht="34.200000000000003" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="8" customFormat="1" ht="68.25" customHeight="1">
-      <c r="A3" s="9" t="s">
+    <row r="4" spans="1:16" s="8" customFormat="1" ht="68.25" customHeight="1">
+      <c r="A4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="11.4" customHeight="1">
-      <c r="A4" s="10" t="s">
+    <row r="5" spans="1:16" ht="11.4" customHeight="1">
+      <c r="A5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I5" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K5" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O4" s="10" t="s">
+      <c r="O5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P5" s="10" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P4" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:P5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
+++ b/APS-Modules/aps-lh/src/main/resources/excelModel/lhhmjh.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\JY-APS\APS-Modules\aps-lh\src\main\resources\excelModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2563EB-4E00-4F46-A3B6-63F46C49A7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F76F22-8F72-4460-B5BF-86E005C27A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -468,9 +468,6 @@
     <t>{afterMaterialType}</t>
   </si>
   <si>
-    <t>{endType}</t>
-  </si>
-  <si>
     <t>{isDryIceClean}</t>
   </si>
   <si>
@@ -484,6 +481,10 @@
   </si>
   <si>
     <t>{remark}</t>
+  </si>
+  <si>
+    <t>{changeType}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1116,22 +1117,22 @@
         <v>57</v>
       </c>
       <c r="K1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="33.75" customHeight="1">
